--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,29 +477,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Герман Греф</t>
+          <t>Herman Gref</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>CEO and Chairman of the Executive Board</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+7 (495) 788-55-55</t>
+          <t>+7 (495) 957-57-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>info@sberbank.ru</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/sberbank/</t>
-        </is>
-      </c>
+          <t>sberbank@sberbank.ru</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>AI-1 (Groq Web Search)</t>
@@ -507,7 +503,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -526,29 +522,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Александр Ведяхин</t>
+          <t>Anton Siluanov</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Первый заместитель председателя Правления</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>info@sberbank.ru</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/sberbank/</t>
-        </is>
-      </c>
+          <t>Chairman of the Supervisory Board</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>AI-1 (Groq Web Search)</t>
@@ -556,7 +540,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -569,35 +553,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Сбербанк  
-   № 1481, Москва</t>
+          <t>Газпромбанк  
+   № 354, Москва</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Лев Хасис</t>
+          <t>Alexei Miller</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Заместитель председателя Правления</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>info@sberbank.ru</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/sberbank/</t>
-        </is>
-      </c>
+          <t>Chairman of the Board of Directors</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>AI-1 (Groq Web Search)</t>
@@ -605,7 +577,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +590,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Сбербанк  
-   № 1481, Москва</t>
+          <t>Газпромбанк  
+   № 354, Москва</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Сергей Мальцев</t>
+          <t>Andrey Akimov</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Член Правления</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>info@sberbank.ru</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/sberbank/</t>
-        </is>
-      </c>
+          <t>Chairman of the Management Board (CEO)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>AI-1 (Groq Web Search)</t>
@@ -654,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -667,35 +627,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Сбербанк  
-   № 1481, Москва</t>
+          <t>Альфа-Банк  
+   № 1326, Москва</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Наталья Алымова</t>
+          <t>Oleg Sysuev</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Директор департамента по связям с инвесторами</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>info@sberbank.ru</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/sberbank/</t>
-        </is>
-      </c>
+          <t>Chairman of the Board of Directors</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>AI-1 (Groq Web Search)</t>
@@ -703,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -716,35 +664,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ВТБ  
-   № 1000, Санкт-Петербург</t>
+          <t>Альфа-Банк  
+   № 1326, Москва</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Андрей Леонидович Костин</t>
+          <t>Vladimir Verkhoshinskiy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Президент - Председатель Правления</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+7 (495) 739-70-00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>info@vtb.ru</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/vtb-bank/</t>
-        </is>
-      </c>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>AI-1 (Groq Web Search)</t>
@@ -752,7 +688,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -765,28 +701,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ВТБ  
-   № 1000, Санкт-Петербург</t>
+          <t>НКЦ (Национальный клиринговый центр)  
+   № 3466-ЦК, Москва</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Дмитрий Юрьевич Пьянов</t>
+          <t>Игорь Леонидович Марич</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Заместитель Президента - Председателя Правления</t>
+          <t>Председатель правления</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+7 (495) 739-70-00</t>
+          <t>+7 495 782-97-94</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>info@vtb.ru</t>
+          <t>info-nkcbank@moex.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -797,7 +733,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -810,30 +746,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ВТБ  
-   № 1000, Санкт-Петербург</t>
+          <t>НКЦ (Национальный клиринговый центр)  
+   № 3466-ЦК, Москва</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Алексей Александрович Токарев</t>
+          <t>Алексей Сергеевич Хавин</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Заместитель Президента - Председателя Правления</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+7 (495) 739-70-00</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>info@vtb.ru</t>
-        </is>
-      </c>
+          <t>+7 495 363-32-32</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
@@ -842,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -851,501 +783,6 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ВТБ  
-   № 1000, Санкт-Петербург</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Владимир Викторович Верхошинский</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Член Правления</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>+7 (495) 739-70-00</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>info@vtb.ru</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ВТБ  
-   № 1000, Санкт-Петербург</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Денис Львович Бортников</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Директор департамента информационных технологий</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>+7 (495) 739-70-00</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>info@vtb.ru</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Газпромбанк  
-   № 354, Москва</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Алексей Борисович Миллер</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Председатель Правления</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>+7 (495) 981-55-55</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>info@gazprombank.ru</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Газпромбанк  
-   № 354, Москва</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Елена Владимировна Борисенко</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Заместитель председателя Правления</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>+7 (495) 981-55-55</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>info@gazprombank.ru</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Газпромбанк  
-   № 354, Москва</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Дмитрий Александрович Жирнов</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Заместитель председателя Правления</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>+7 (495) 981-55-55</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>info@gazprombank.ru</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Газпромбанк  
-   № 354, Москва</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Игорь Викторович Антонов</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Член Правления</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>+7 (495) 981-55-55</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>info@gazprombank.ru</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Газпромбанк  
-   № 354, Москва</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Сергей Викторович Попов</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Директор департамента корпоративных финансов</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>+7 (495) 981-55-55</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>info@gazprombank.ru</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Альфа-Банк  
-   № 1326, Москва</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Владимир Верхошинский</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Председатель Правления</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>info@alfabank.ru</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Альфа-Банк  
-   № 1326, Москва</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Андрей Соколов</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Заместитель председателя Правления</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>info@alfabank.ru</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Альфа-Банк  
-   № 1326, Москва</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Дмитрий Ракitin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Член Правления</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>info@alfabank.ru</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Альфа-Банк  
-   № 1326, Москва</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Алексей Чураков</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Директор департамента корпоративных клиентов</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-55-55</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>info@alfabank.ru</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AI-1 (Groq Web Search)</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Найдено</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
